--- a/artfynd/A 43056-2025 artfynd.xlsx
+++ b/artfynd/A 43056-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131258593</v>
+        <v>131258599</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102621</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,17 +703,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661114</v>
+        <v>661386</v>
       </c>
       <c r="R2" t="n">
-        <v>6660714</v>
+        <v>6660947</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,27 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131258599</v>
+        <v>131258593</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,29 +822,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661386</v>
+        <v>661114</v>
       </c>
       <c r="R3" t="n">
-        <v>6660947</v>
+        <v>6660714</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
         <v>131258596</v>
       </c>
       <c r="B4" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>131258602</v>
       </c>
       <c r="B5" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>131258595</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>131258598</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>131258603</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>131258597</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>131258605</v>
       </c>
       <c r="B10" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>131258600</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>131258594</v>
       </c>
       <c r="B12" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>131258604</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43056-2025 artfynd.xlsx
+++ b/artfynd/A 43056-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131258599</v>
+        <v>131258593</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,29 +703,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661386</v>
+        <v>661114</v>
       </c>
       <c r="R2" t="n">
-        <v>6660947</v>
+        <v>6660714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,27 +782,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131258593</v>
+        <v>131258599</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,17 +810,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661114</v>
+        <v>661386</v>
       </c>
       <c r="R3" t="n">
-        <v>6660714</v>
+        <v>6660947</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,45 +901,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131258596</v>
+        <v>131258602</v>
       </c>
       <c r="B4" t="n">
-        <v>91816</v>
+        <v>92539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östmossen, Upl</t>
+          <t>Vitmossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661129</v>
+        <v>661212</v>
       </c>
       <c r="R4" t="n">
-        <v>6660729</v>
+        <v>6660675</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,45 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131258602</v>
+        <v>131258596</v>
       </c>
       <c r="B5" t="n">
-        <v>92538</v>
+        <v>91817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vitmossen, Upl</t>
+          <t>Östmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661212</v>
+        <v>661129</v>
       </c>
       <c r="R5" t="n">
-        <v>6660675</v>
+        <v>6660729</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1118,7 @@
         <v>131258595</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>131258598</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>131258603</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>131258597</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>131258605</v>
       </c>
       <c r="B10" t="n">
-        <v>92275</v>
+        <v>92276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>131258600</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>131258594</v>
       </c>
       <c r="B12" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>131258604</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43056-2025 artfynd.xlsx
+++ b/artfynd/A 43056-2025 artfynd.xlsx
@@ -901,45 +901,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131258602</v>
+        <v>131258595</v>
       </c>
       <c r="B4" t="n">
-        <v>92539</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vitmossen, Upl</t>
+          <t>Östmossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661212</v>
+        <v>661120</v>
       </c>
       <c r="R4" t="n">
-        <v>6660675</v>
+        <v>6660717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1115,45 +1115,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131258595</v>
+        <v>131258602</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>92539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östmossen, Upl</t>
+          <t>Vitmossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661120</v>
+        <v>661212</v>
       </c>
       <c r="R6" t="n">
-        <v>6660717</v>
+        <v>6660675</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 43056-2025 artfynd.xlsx
+++ b/artfynd/A 43056-2025 artfynd.xlsx
@@ -901,45 +901,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131258595</v>
+        <v>131258602</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>92539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östmossen, Upl</t>
+          <t>Vitmossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661120</v>
+        <v>661212</v>
       </c>
       <c r="R4" t="n">
-        <v>6660717</v>
+        <v>6660675</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1115,45 +1115,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131258602</v>
+        <v>131258595</v>
       </c>
       <c r="B6" t="n">
-        <v>92539</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vitmossen, Upl</t>
+          <t>Östmossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661212</v>
+        <v>661120</v>
       </c>
       <c r="R6" t="n">
-        <v>6660675</v>
+        <v>6660717</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 43056-2025 artfynd.xlsx
+++ b/artfynd/A 43056-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131258593</v>
+        <v>131258594</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661114</v>
+        <v>661128</v>
       </c>
       <c r="R2" t="n">
-        <v>6660714</v>
+        <v>6660716</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,57 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131258599</v>
+        <v>131258596</v>
       </c>
       <c r="B3" t="n">
-        <v>57743</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661386</v>
+        <v>661129</v>
       </c>
       <c r="R3" t="n">
-        <v>6660947</v>
+        <v>6660729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131258596</v>
+        <v>131258605</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661129</v>
+        <v>661007</v>
       </c>
       <c r="R4" t="n">
-        <v>6660729</v>
+        <v>6660690</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +999,7 @@
         <v>131258602</v>
       </c>
       <c r="B5" t="n">
-        <v>92555</v>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131258595</v>
+        <v>131258593</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1150,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661120</v>
+        <v>661114</v>
       </c>
       <c r="R6" t="n">
-        <v>6660717</v>
+        <v>6660714</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131258598</v>
+        <v>131258595</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1257,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661168</v>
+        <v>661120</v>
       </c>
       <c r="R7" t="n">
-        <v>6660879</v>
+        <v>6660717</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131258603</v>
+        <v>131258597</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1360,14 +1348,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vitmossen, Upl</t>
+          <t>Östmossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661213</v>
+        <v>661122</v>
       </c>
       <c r="R8" t="n">
-        <v>6660650</v>
+        <v>6660729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1409,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131258597</v>
+        <v>131258598</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1471,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661122</v>
+        <v>661168</v>
       </c>
       <c r="R9" t="n">
-        <v>6660729</v>
+        <v>6660879</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1516,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131258605</v>
+        <v>131258600</v>
       </c>
       <c r="B10" t="n">
-        <v>92292</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661007</v>
+        <v>661222</v>
       </c>
       <c r="R10" t="n">
-        <v>6660690</v>
+        <v>6660764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1623,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,14 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131258600</v>
+        <v>131258603</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1681,14 +1669,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östmossen, Upl</t>
+          <t>Vitmossen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661222</v>
+        <v>661213</v>
       </c>
       <c r="R11" t="n">
-        <v>6660764</v>
+        <v>6660650</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1730,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131258594</v>
+        <v>131258604</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1792,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661128</v>
+        <v>661077</v>
       </c>
       <c r="R12" t="n">
-        <v>6660716</v>
+        <v>6660650</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1837,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131258604</v>
+        <v>131258599</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1875,16 +1863,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1892,17 +1880,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Östmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661077</v>
+        <v>661386</v>
       </c>
       <c r="R13" t="n">
-        <v>6660650</v>
+        <v>6660947</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
